--- a/artfynd/A 27388-2026 artfynd.xlsx
+++ b/artfynd/A 27388-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137280211</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137280508</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137282606</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>137280294</v>
       </c>
       <c r="B5" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>137280232</v>
       </c>
       <c r="B6" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>137282028</v>
       </c>
       <c r="B7" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>137282974</v>
       </c>
       <c r="B8" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 27388-2026 artfynd.xlsx
+++ b/artfynd/A 27388-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137280211</v>
       </c>
       <c r="B2" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137280508</v>
       </c>
       <c r="B3" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27388-2026 artfynd.xlsx
+++ b/artfynd/A 27388-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137280211</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137280508</v>
       </c>
       <c r="B3" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137282606</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27388-2026 artfynd.xlsx
+++ b/artfynd/A 27388-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137280211</v>
       </c>
       <c r="B2" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137280508</v>
       </c>
       <c r="B3" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27388-2026 artfynd.xlsx
+++ b/artfynd/A 27388-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137280211</v>
       </c>
       <c r="B2" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137280508</v>
       </c>
       <c r="B3" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137282606</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27388-2026 artfynd.xlsx
+++ b/artfynd/A 27388-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137280211</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137280508</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27388-2026 artfynd.xlsx
+++ b/artfynd/A 27388-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137280211</v>
       </c>
       <c r="B2" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137280508</v>
       </c>
       <c r="B3" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27388-2026 artfynd.xlsx
+++ b/artfynd/A 27388-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137280211</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137280508</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27388-2026 artfynd.xlsx
+++ b/artfynd/A 27388-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137280211</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137280508</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137282606</v>
       </c>
       <c r="B4" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
